--- a/outputs/Block4_Diagnostics_v12.xlsx
+++ b/outputs/Block4_Diagnostics_v12.xlsx
@@ -256,19 +256,19 @@
     <t>Integer</t>
   </si>
   <si>
+    <t>Very high sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate-low sensitivity</t>
+  </si>
+  <si>
+    <t>Low sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate sensitivity</t>
+  </si>
+  <si>
     <t>High sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate sensitivity</t>
-  </si>
-  <si>
-    <t>Low sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate-low sensitivity</t>
-  </si>
-  <si>
-    <t>Very high sensitivity</t>
   </si>
 </sst>
 </file>
@@ -729,31 +729,31 @@
         <v>72</v>
       </c>
       <c r="C2">
-        <v>0.5015439999999998</v>
+        <v>0.5025559999999998</v>
       </c>
       <c r="D2">
-        <v>0.4872199999999994</v>
+        <v>0.4879279999999993</v>
       </c>
       <c r="E2">
-        <v>0.487434430017597</v>
+        <v>0.4850537176443364</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.4953563430886915</v>
+        <v>0.4962370216909646</v>
       </c>
       <c r="H2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="I2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -768,13 +768,13 @@
         <v>77</v>
       </c>
       <c r="P2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="S2" t="s">
         <v>78</v>
@@ -789,16 +789,16 @@
         <v>6</v>
       </c>
       <c r="W2">
-        <v>0.4953563430886915</v>
+        <v>0.4962370216909646</v>
       </c>
       <c r="X2">
-        <v>0.01396502707705438</v>
+        <v>0.02444487447156363</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>1.055164654914086</v>
+        <v>1.8469973165026</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -807,7 +807,7 @@
         <v>0.317384338170467</v>
       </c>
       <c r="AC2">
-        <v>50.36583963684151</v>
+        <v>30.10291257195357</v>
       </c>
       <c r="AD2" t="s">
         <v>80</v>
@@ -821,31 +821,31 @@
         <v>72</v>
       </c>
       <c r="C3">
-        <v>0.4696599999999989</v>
+        <v>0.4686639999999987</v>
       </c>
       <c r="D3">
-        <v>0.4840119999999993</v>
+        <v>0.4831359999999993</v>
       </c>
       <c r="E3">
-        <v>0.485114447962659</v>
+        <v>0.4848653204771308</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4758597523032031</v>
+        <v>0.4749155896970425</v>
       </c>
       <c r="H3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="I3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -860,13 +860,13 @@
         <v>77</v>
       </c>
       <c r="P3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="S3" t="s">
         <v>78</v>
@@ -881,16 +881,16 @@
         <v>6</v>
       </c>
       <c r="W3">
-        <v>0.4758597523032031</v>
+        <v>0.4749155896970425</v>
       </c>
       <c r="X3">
-        <v>0.01438112246894896</v>
+        <v>0.02479748585957076</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.351420773874486</v>
+        <v>2.330265777434267</v>
       </c>
       <c r="AA3">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0.2764021804054501</v>
       </c>
       <c r="AC3">
-        <v>41.5437331399677</v>
+        <v>21.98801276749871</v>
       </c>
       <c r="AD3" t="s">
         <v>80</v>
@@ -913,25 +913,25 @@
         <v>73</v>
       </c>
       <c r="C4">
-        <v>1.092</v>
+        <v>1.128</v>
       </c>
       <c r="D4">
-        <v>1.224</v>
+        <v>1.252</v>
       </c>
       <c r="E4">
-        <v>0.5513716620292705</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="F4">
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.155708792388448</v>
+        <v>1.187847653455815</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>0.5513716620292705</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="L4">
         <v>0.8200692764238203</v>
@@ -946,10 +946,10 @@
         <v>77</v>
       </c>
       <c r="P4">
-        <v>0.5680132525146347</v>
+        <v>1.036948324347409</v>
       </c>
       <c r="Q4">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -958,37 +958,37 @@
         <v>79</v>
       </c>
       <c r="T4">
-        <v>0.01664159048536429</v>
+        <v>0.01087699950497645</v>
       </c>
       <c r="U4">
-        <v>0.4319867474853653</v>
+        <v>-0.03694832434740891</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>1.155708792388448</v>
+        <v>1.187847653455815</v>
       </c>
       <c r="X4">
-        <v>0.6043371303591779</v>
+        <v>0.1617763286133824</v>
       </c>
       <c r="Y4">
-        <v>0.4486283379707295</v>
+        <v>0.02607132484243246</v>
       </c>
       <c r="Z4">
-        <v>0.7369342416955152</v>
+        <v>0.1972715394470829</v>
       </c>
       <c r="AA4">
-        <v>0.5470615115921911</v>
+        <v>0.03179161272340916</v>
       </c>
       <c r="AB4">
         <v>0.7455175240216548</v>
       </c>
       <c r="AC4">
-        <v>51.14636374435788</v>
+        <v>86.99204005901876</v>
       </c>
       <c r="AD4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -999,25 +999,25 @@
         <v>73</v>
       </c>
       <c r="C5">
-        <v>1.276</v>
+        <v>1.412</v>
       </c>
       <c r="D5">
-        <v>1.788</v>
+        <v>1.808</v>
       </c>
       <c r="E5">
-        <v>0.7074963699328916</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="F5">
         <v>2.2</v>
       </c>
       <c r="G5">
-        <v>1.523112891688526</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>0.7074963699328916</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="L5">
         <v>1.746417103282563</v>
@@ -1032,49 +1032,49 @@
         <v>77</v>
       </c>
       <c r="P5">
-        <v>0.7288501421143858</v>
+        <v>1.717926703142854</v>
       </c>
       <c r="Q5">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="s">
         <v>79</v>
       </c>
       <c r="T5">
-        <v>0.02135377218149426</v>
+        <v>0.01802007627663649</v>
       </c>
       <c r="U5">
-        <v>0.2711498578856142</v>
+        <v>0.2820732968571464</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>1.523112891688526</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="X5">
-        <v>0.8156165217556348</v>
+        <v>0.09678024970087273</v>
       </c>
       <c r="Y5">
-        <v>0.2925036300671084</v>
+        <v>0.3000933731337829</v>
       </c>
       <c r="Z5">
-        <v>0.4670227520233302</v>
+        <v>0.05541645779748992</v>
       </c>
       <c r="AA5">
-        <v>0.167487840972995</v>
+        <v>0.1718337346615124</v>
       </c>
       <c r="AB5">
         <v>0.7593117840358968</v>
       </c>
       <c r="AC5">
-        <v>69.61531963599649</v>
+        <v>90.83163983910151</v>
       </c>
       <c r="AD5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -1085,25 +1085,25 @@
         <v>73</v>
       </c>
       <c r="C6">
-        <v>7.9</v>
+        <v>7.968</v>
       </c>
       <c r="D6">
-        <v>8.827999999999999</v>
+        <v>8.868</v>
       </c>
       <c r="E6">
-        <v>7.820194910667125</v>
+        <v>10.0582691946606</v>
       </c>
       <c r="F6">
         <v>9.4</v>
       </c>
       <c r="G6">
-        <v>8.347892116185454</v>
+        <v>8.402378129921239</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>7.820194910667125</v>
+        <v>10.0582691946606</v>
       </c>
       <c r="L6">
         <v>4.467028425282805</v>
@@ -1118,49 +1118,49 @@
         <v>77</v>
       </c>
       <c r="P6">
-        <v>8.056225323873495</v>
+        <v>10.16489315578537</v>
       </c>
       <c r="Q6">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S6" t="s">
         <v>79</v>
       </c>
       <c r="T6">
-        <v>0.23603041320637</v>
+        <v>0.1066239611247735</v>
       </c>
       <c r="U6">
-        <v>-0.05622532387349466</v>
+        <v>-0.1648931557853732</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>8.347892116185454</v>
+        <v>8.402378129921239</v>
       </c>
       <c r="X6">
-        <v>0.5276972055183293</v>
+        <v>1.655891064739361</v>
       </c>
       <c r="Y6">
-        <v>0.1798050893328753</v>
+        <v>0.05826919466059977</v>
       </c>
       <c r="Z6">
-        <v>0.1181315978496199</v>
+        <v>0.3706918575595425</v>
       </c>
       <c r="AA6">
-        <v>0.04025161073862921</v>
+        <v>0.01304428562191448</v>
       </c>
       <c r="AB6">
         <v>0.911638454139348</v>
       </c>
       <c r="AC6">
-        <v>91.31331214761543</v>
+        <v>78.23013869485108</v>
       </c>
       <c r="AD6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1171,25 +1171,25 @@
         <v>73</v>
       </c>
       <c r="C7">
-        <v>3.516</v>
+        <v>3.54</v>
       </c>
       <c r="D7">
-        <v>4.924</v>
+        <v>4.812</v>
       </c>
       <c r="E7">
-        <v>5.173756282914196</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7">
-        <v>4.195560452143448</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>5.173756282914196</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="L7">
         <v>2.262338789582505</v>
@@ -1204,49 +1204,49 @@
         <v>77</v>
       </c>
       <c r="P7">
-        <v>5.329911448768128</v>
+        <v>5.645415907992541</v>
       </c>
       <c r="Q7">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S7" t="s">
         <v>79</v>
       </c>
       <c r="T7">
-        <v>0.1561551658539315</v>
+        <v>0.05921720937758934</v>
       </c>
       <c r="U7">
-        <v>-0.3299114487681276</v>
+        <v>0.3545840920074594</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>4.195560452143448</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="X7">
-        <v>0.9781958307707486</v>
+        <v>1.432277608326268</v>
       </c>
       <c r="Y7">
-        <v>0.1737562829141961</v>
+        <v>0.4138013013850488</v>
       </c>
       <c r="Z7">
-        <v>0.4323825570578075</v>
+        <v>0.633095986737947</v>
       </c>
       <c r="AA7">
-        <v>0.07680382960956141</v>
+        <v>0.1829086356519627</v>
       </c>
       <c r="AB7">
         <v>0.452467757916501</v>
       </c>
       <c r="AC7">
-        <v>73.49667620805681</v>
+        <v>62.15552874778314</v>
       </c>
       <c r="AD7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1257,25 +1257,25 @@
         <v>73</v>
       </c>
       <c r="C8">
-        <v>13.792</v>
+        <v>13.58</v>
       </c>
       <c r="D8">
-        <v>14.964</v>
+        <v>14.788</v>
       </c>
       <c r="E8">
-        <v>18.4418098343119</v>
+        <v>19.01148659179185</v>
       </c>
       <c r="F8">
         <v>14.6</v>
       </c>
       <c r="G8">
-        <v>14.35765685363077</v>
+        <v>14.16303197882762</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>18.4418098343119</v>
+        <v>19.01148659179185</v>
       </c>
       <c r="L8">
         <v>5.333756871724871</v>
@@ -1290,10 +1290,10 @@
         <v>77</v>
       </c>
       <c r="P8">
-        <v>18.99842358181946</v>
+        <v>19.21302027199633</v>
       </c>
       <c r="Q8">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R8">
         <v>19</v>
@@ -1302,37 +1302,37 @@
         <v>79</v>
       </c>
       <c r="T8">
-        <v>0.556613747507555</v>
+        <v>0.2015336802044807</v>
       </c>
       <c r="U8">
-        <v>0.001576418180540884</v>
+        <v>-0.2130202719963314</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>14.35765685363077</v>
+        <v>14.16303197882762</v>
       </c>
       <c r="X8">
-        <v>4.084152980681136</v>
+        <v>4.848454612964233</v>
       </c>
       <c r="Y8">
-        <v>0.5581901656880959</v>
+        <v>0.01148659179185074</v>
       </c>
       <c r="Z8">
-        <v>0.7657178755807014</v>
+        <v>0.909013052069676</v>
       </c>
       <c r="AA8">
-        <v>0.1046523452628961</v>
+        <v>0.00215356493895383</v>
       </c>
       <c r="AB8">
         <v>1.088521810556096</v>
       </c>
       <c r="AC8">
-        <v>58.6053064371732</v>
+        <v>55.34343008256245</v>
       </c>
       <c r="AD8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1343,25 +1343,25 @@
         <v>73</v>
       </c>
       <c r="C9">
-        <v>2.568</v>
+        <v>3.184</v>
       </c>
       <c r="D9">
-        <v>3.732</v>
+        <v>4.004</v>
       </c>
       <c r="E9">
-        <v>-3.223234081728676</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="F9">
         <v>5.8</v>
       </c>
       <c r="G9">
-        <v>3.129795714698134</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="L9">
         <v>7.059923274159115</v>
@@ -1376,46 +1376,46 @@
         <v>77</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.566812662552681</v>
       </c>
       <c r="Q9">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="s">
         <v>79</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.01643497574066832</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>0.433187337447319</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>3.129795714698134</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="X9">
-        <v>3.129795714698134</v>
+        <v>2.029389053782892</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>0.4496223131879873</v>
       </c>
       <c r="Z9">
-        <v>0.4433186584553801</v>
+        <v>0.2874519984106493</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.06368657218042365</v>
       </c>
       <c r="AB9">
         <v>0.9289372729156731</v>
       </c>
       <c r="AC9">
-        <v>74.96437929576021</v>
+        <v>81.12864354622022</v>
       </c>
       <c r="AD9" t="s">
         <v>81</v>
@@ -1429,25 +1429,25 @@
         <v>73</v>
       </c>
       <c r="C10">
-        <v>173.312</v>
+        <v>172.984</v>
       </c>
       <c r="D10">
-        <v>170.552</v>
+        <v>170.488</v>
       </c>
       <c r="E10">
-        <v>176.0063243272117</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="F10">
         <v>169.2</v>
       </c>
       <c r="G10">
-        <v>171.9799070682415</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>176.0063243272117</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="L10">
         <v>4.764861070548267</v>
@@ -1462,49 +1462,49 @@
         <v>77</v>
       </c>
       <c r="P10">
-        <v>181.3185762509099</v>
+        <v>174.4769462223457</v>
       </c>
       <c r="Q10">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R10">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="S10" t="s">
         <v>79</v>
       </c>
       <c r="T10">
-        <v>5.31225192369817</v>
+        <v>1.830164158743969</v>
       </c>
       <c r="U10">
-        <v>-0.3185762509098993</v>
+        <v>-0.4769462223457026</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>171.9799070682415</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="X10">
-        <v>4.026417258970184</v>
+        <v>0.8674574105832846</v>
       </c>
       <c r="Y10">
-        <v>4.993675672788271</v>
+        <v>1.353217936398266</v>
       </c>
       <c r="Z10">
-        <v>0.845023013127828</v>
+        <v>0.1820530331818197</v>
       </c>
       <c r="AA10">
-        <v>1.04802125368446</v>
+        <v>0.2839994527358924</v>
       </c>
       <c r="AB10">
         <v>0.3609743235263839</v>
       </c>
       <c r="AC10">
-        <v>40.00873433552916</v>
+        <v>80.43391422492162</v>
       </c>
       <c r="AD10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1515,25 +1515,25 @@
         <v>73</v>
       </c>
       <c r="C11">
-        <v>3.096</v>
+        <v>3.948</v>
       </c>
       <c r="D11">
-        <v>4.516</v>
+        <v>4.92</v>
       </c>
       <c r="E11">
-        <v>-5.436536811828134</v>
+        <v>1.16567981478854</v>
       </c>
       <c r="F11">
         <v>7.4</v>
       </c>
       <c r="G11">
-        <v>3.781352160542397</v>
+        <v>4.417128380314937</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1.16567981478854</v>
       </c>
       <c r="L11">
         <v>9.933150479214353</v>
@@ -1548,49 +1548,49 @@
         <v>77</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.178036751837105</v>
       </c>
       <c r="Q11">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="s">
         <v>79</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.01235693704856522</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>-0.1780367518371049</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>3.781352160542397</v>
+        <v>4.417128380314937</v>
       </c>
       <c r="X11">
-        <v>3.781352160542397</v>
+        <v>3.251448565526397</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>0.1656798147885397</v>
       </c>
       <c r="Z11">
-        <v>0.3806800439050106</v>
+        <v>0.3273330623884362</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.01667948302356171</v>
       </c>
       <c r="AB11">
         <v>0.9643835416712964</v>
       </c>
       <c r="AC11">
-        <v>78.07954833544376</v>
+        <v>80.36396477336831</v>
       </c>
       <c r="AD11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -1601,25 +1601,25 @@
         <v>73</v>
       </c>
       <c r="C12">
-        <v>3.732</v>
+        <v>3.692</v>
       </c>
       <c r="D12">
         <v>3.192</v>
       </c>
       <c r="E12">
-        <v>3.990456585529889</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3.471373122047258</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>3.990456585529889</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="L12">
         <v>0.887818750560327</v>
@@ -1634,46 +1634,46 @@
         <v>77</v>
       </c>
       <c r="P12">
-        <v>3.736401375072155</v>
+        <v>3.440193613933819</v>
       </c>
       <c r="Q12">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S12" t="s">
         <v>79</v>
       </c>
       <c r="T12">
-        <v>-0.2540552104577345</v>
+        <v>-0.03526554980344976</v>
       </c>
       <c r="U12">
-        <v>0.263598624927845</v>
+        <v>-0.4401936139338187</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>3.471373122047258</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="X12">
-        <v>0.5190834634826316</v>
+        <v>0.0247803470268444</v>
       </c>
       <c r="Y12">
-        <v>0.009543414470110534</v>
+        <v>0.4754591637372685</v>
       </c>
       <c r="Z12">
-        <v>0.5846727872722035</v>
+        <v>0.02791149320872625</v>
       </c>
       <c r="AA12">
-        <v>0.01074928240036316</v>
+        <v>0.5355362943587225</v>
       </c>
       <c r="AB12">
         <v>0.3551275002241308</v>
       </c>
       <c r="AC12">
-        <v>68.12679664600398</v>
+        <v>81.41748166151876</v>
       </c>
       <c r="AD12" t="s">
         <v>81</v>
@@ -1687,25 +1687,25 @@
         <v>73</v>
       </c>
       <c r="C13">
-        <v>1.88</v>
+        <v>1.832</v>
       </c>
       <c r="D13">
-        <v>1.824</v>
+        <v>1.772</v>
       </c>
       <c r="E13">
-        <v>3.02590709890818</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="F13">
         <v>1.6</v>
       </c>
       <c r="G13">
-        <v>1.852972027471568</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>3.02590709890818</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="L13">
         <v>1.198624596172324</v>
@@ -1720,49 +1720,49 @@
         <v>77</v>
       </c>
       <c r="P13">
-        <v>2.83326060636738</v>
+        <v>2.528722469358031</v>
       </c>
       <c r="Q13">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13" t="s">
         <v>79</v>
       </c>
       <c r="T13">
-        <v>-0.1926464925408</v>
+        <v>-0.02592202596419435</v>
       </c>
       <c r="U13">
-        <v>0.1667393936326196</v>
+        <v>-0.5287224693580312</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>1.852972027471568</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="X13">
-        <v>1.172935071436613</v>
+        <v>0.7516030373169746</v>
       </c>
       <c r="Y13">
-        <v>0.02590709890818044</v>
+        <v>0.5546444953222256</v>
       </c>
       <c r="Z13">
-        <v>0.9785674974318499</v>
+        <v>0.627054575483547</v>
       </c>
       <c r="AA13">
-        <v>0.02161402243113641</v>
+        <v>0.4627341179994319</v>
       </c>
       <c r="AB13">
         <v>0.7491403726077025</v>
       </c>
       <c r="AC13">
-        <v>52.53798358234432</v>
+        <v>56.57842736664286</v>
       </c>
       <c r="AD13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1773,25 +1773,25 @@
         <v>73</v>
       </c>
       <c r="C14">
-        <v>13.488</v>
+        <v>13.316</v>
       </c>
       <c r="D14">
-        <v>12.544</v>
+        <v>12.472</v>
       </c>
       <c r="E14">
-        <v>15.02106749310035</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="F14">
         <v>11.8</v>
       </c>
       <c r="G14">
-        <v>13.03238560594928</v>
+        <v>12.9086498426072</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>15.02106749310035</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="L14">
         <v>3.125306797245826</v>
@@ -1806,49 +1806,49 @@
         <v>77</v>
       </c>
       <c r="P14">
-        <v>14.06474072159816</v>
+        <v>12.85213593315269</v>
       </c>
       <c r="Q14">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S14" t="s">
         <v>79</v>
       </c>
       <c r="T14">
-        <v>-0.956326771502189</v>
+        <v>-0.1317477126855753</v>
       </c>
       <c r="U14">
-        <v>-0.06474072159816124</v>
+        <v>0.1478640668473066</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>13.03238560594928</v>
+        <v>12.9086498426072</v>
       </c>
       <c r="X14">
-        <v>1.988681887151071</v>
+        <v>0.07523380323107176</v>
       </c>
       <c r="Y14">
-        <v>1.02106749310035</v>
+        <v>0.01611635416173129</v>
       </c>
       <c r="Z14">
-        <v>0.6363157335156967</v>
+        <v>0.02407245371794266</v>
       </c>
       <c r="AA14">
-        <v>0.3267095230459183</v>
+        <v>0.005156727069462051</v>
       </c>
       <c r="AB14">
         <v>0.6511055827595471</v>
       </c>
       <c r="AC14">
-        <v>58.9810747875693</v>
+        <v>98.2699453837879</v>
       </c>
       <c r="AD14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -1859,25 +1859,25 @@
         <v>73</v>
       </c>
       <c r="C15">
-        <v>8.456</v>
+        <v>8.612</v>
       </c>
       <c r="D15">
-        <v>6.348</v>
+        <v>6.564</v>
       </c>
       <c r="E15">
-        <v>4.233012499265572</v>
+        <v>3.808811132083866</v>
       </c>
       <c r="F15">
         <v>6.6</v>
       </c>
       <c r="G15">
-        <v>7.438589891251147</v>
+        <v>7.623548433245896</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>4.233012499265572</v>
+        <v>3.808811132083866</v>
       </c>
       <c r="L15">
         <v>4.673523904256721</v>
@@ -1892,10 +1892,10 @@
         <v>77</v>
       </c>
       <c r="P15">
-        <v>3.963514796854575</v>
+        <v>3.770163053558897</v>
       </c>
       <c r="Q15">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R15">
         <v>4</v>
@@ -1904,37 +1904,37 @@
         <v>79</v>
       </c>
       <c r="T15">
-        <v>-0.2694977024109964</v>
+        <v>-0.03864807852496854</v>
       </c>
       <c r="U15">
-        <v>0.0364852031454248</v>
+        <v>0.229836946441103</v>
       </c>
       <c r="V15" t="s">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7.438589891251147</v>
+        <v>7.623548433245896</v>
       </c>
       <c r="X15">
-        <v>3.205577391985575</v>
+        <v>3.81473730116203</v>
       </c>
       <c r="Y15">
-        <v>0.2330124992655715</v>
+        <v>0.1911888679161344</v>
       </c>
       <c r="Z15">
-        <v>0.6859015718451517</v>
+        <v>0.816244311425797</v>
       </c>
       <c r="AA15">
-        <v>0.04985798811328214</v>
+        <v>0.04090893121184135</v>
       </c>
       <c r="AB15">
         <v>0.5563718933638954</v>
       </c>
       <c r="AC15">
-        <v>62.92124521541888</v>
+        <v>57.99131498158366</v>
       </c>
       <c r="AD15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -1945,25 +1945,25 @@
         <v>73</v>
       </c>
       <c r="C16">
-        <v>15.112</v>
+        <v>15.048</v>
       </c>
       <c r="D16">
-        <v>15.028</v>
+        <v>14.824</v>
       </c>
       <c r="E16">
-        <v>17.90152433308469</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="F16">
         <v>14.2</v>
       </c>
       <c r="G16">
-        <v>15.07145804120735</v>
+        <v>14.93988810988627</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>17.90152433308469</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="L16">
         <v>6.129350049043507</v>
@@ -1978,49 +1978,49 @@
         <v>77</v>
       </c>
       <c r="P16">
-        <v>16.76181126154098</v>
+        <v>14.85295632081913</v>
       </c>
       <c r="Q16">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R16">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S16" t="s">
         <v>79</v>
       </c>
       <c r="T16">
-        <v>-1.13971307154371</v>
+        <v>-0.152258195218657</v>
       </c>
       <c r="U16">
-        <v>0.2381887384590158</v>
+        <v>0.1470436791808698</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>15.07145804120735</v>
+        <v>14.93988810988627</v>
       </c>
       <c r="X16">
-        <v>2.830066291877342</v>
+        <v>0.06532640615151664</v>
       </c>
       <c r="Y16">
-        <v>0.9015243330846943</v>
+        <v>0.00521451603778722</v>
       </c>
       <c r="Z16">
-        <v>0.4617237177241946</v>
+        <v>0.01065796628171219</v>
       </c>
       <c r="AA16">
-        <v>0.1470831859611899</v>
+        <v>0.0008507453475594778</v>
       </c>
       <c r="AB16">
         <v>0.972912706197382</v>
       </c>
       <c r="AC16">
-        <v>70.35618198382974</v>
+        <v>99.2800601772977</v>
       </c>
       <c r="AD16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:30">
@@ -2031,25 +2031,25 @@
         <v>73</v>
       </c>
       <c r="C17">
-        <v>7.252</v>
+        <v>7.352</v>
       </c>
       <c r="D17">
-        <v>5.608</v>
+        <v>5.764</v>
       </c>
       <c r="E17">
-        <v>4.766317009415515</v>
+        <v>4.801946011202828</v>
       </c>
       <c r="F17">
         <v>5.8</v>
       </c>
       <c r="G17">
-        <v>6.458535949343873</v>
+        <v>6.585563921872306</v>
       </c>
       <c r="J17" t="s">
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.766317009415515</v>
+        <v>4.801946011202828</v>
       </c>
       <c r="L17">
         <v>3.997862832988686</v>
@@ -2064,49 +2064,49 @@
         <v>77</v>
       </c>
       <c r="P17">
-        <v>4.462866102237046</v>
+        <v>4.753220574294097</v>
       </c>
       <c r="Q17">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S17" t="s">
         <v>79</v>
       </c>
       <c r="T17">
-        <v>-0.3034509071784681</v>
+        <v>-0.04872543690873066</v>
       </c>
       <c r="U17">
-        <v>-0.4628661022370464</v>
+        <v>0.2467794257059026</v>
       </c>
       <c r="V17" t="s">
         <v>6</v>
       </c>
       <c r="W17">
-        <v>6.458535949343873</v>
+        <v>6.585563921872306</v>
       </c>
       <c r="X17">
-        <v>1.692218939928359</v>
+        <v>1.783617910669478</v>
       </c>
       <c r="Y17">
-        <v>0.7663170094155145</v>
+        <v>0.198053988797172</v>
       </c>
       <c r="Z17">
-        <v>0.4232808904709982</v>
+        <v>0.446142848111699</v>
       </c>
       <c r="AA17">
-        <v>0.1916816662873444</v>
+        <v>0.04953996599455929</v>
       </c>
       <c r="AB17">
         <v>0.5966959452221919</v>
       </c>
       <c r="AC17">
-        <v>71.01911200459742</v>
+        <v>73.54065235742672</v>
       </c>
       <c r="AD17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:30">
@@ -2117,25 +2117,25 @@
         <v>73</v>
       </c>
       <c r="C18">
-        <v>173.296</v>
+        <v>172.1</v>
       </c>
       <c r="D18">
-        <v>175.72</v>
+        <v>175.156</v>
       </c>
       <c r="E18">
-        <v>182.3239848953666</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="F18">
         <v>172.6</v>
       </c>
       <c r="G18">
-        <v>174.4659250965879</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="J18" t="s">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>182.3239848953666</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="L18">
         <v>24.70132137894479</v>
@@ -2150,49 +2150,49 @@
         <v>77</v>
       </c>
       <c r="P18">
-        <v>170.7162008332492</v>
+        <v>173.8081494148196</v>
       </c>
       <c r="Q18">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R18">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="S18" t="s">
         <v>79</v>
       </c>
       <c r="T18">
-        <v>-11.60778406211739</v>
+        <v>-1.781713658384717</v>
       </c>
       <c r="U18">
-        <v>0.2837991667507822</v>
+        <v>0.1918505851803616</v>
       </c>
       <c r="V18" t="s">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>174.4659250965879</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="X18">
-        <v>7.858059798778754</v>
+        <v>2.014908000938448</v>
       </c>
       <c r="Y18">
-        <v>11.32398489536661</v>
+        <v>1.589863073204356</v>
       </c>
       <c r="Z18">
-        <v>0.3181230541568072</v>
+        <v>0.08157085890376452</v>
       </c>
       <c r="AA18">
-        <v>0.4584364019092145</v>
+        <v>0.06436348277948976</v>
       </c>
       <c r="AB18">
         <v>1.320926276948919</v>
       </c>
       <c r="AC18">
-        <v>69.26484290771914</v>
+        <v>92.72349650896915</v>
       </c>
       <c r="AD18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:30">
@@ -2203,25 +2203,25 @@
         <v>73</v>
       </c>
       <c r="C19">
-        <v>5.232</v>
+        <v>5.304</v>
       </c>
       <c r="D19">
-        <v>4.208</v>
+        <v>4.316</v>
       </c>
       <c r="E19">
-        <v>3.696547591818899</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="F19">
         <v>4.4</v>
       </c>
       <c r="G19">
-        <v>4.737774216622949</v>
+        <v>4.827149341819798</v>
       </c>
       <c r="J19" t="s">
         <v>4</v>
       </c>
       <c r="K19">
-        <v>3.696547591818899</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="L19">
         <v>2.858585552684069</v>
@@ -2236,46 +2236,46 @@
         <v>77</v>
       </c>
       <c r="P19">
-        <v>3.461204303080457</v>
+        <v>3.994458620063688</v>
       </c>
       <c r="Q19">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19" t="s">
         <v>79</v>
       </c>
       <c r="T19">
-        <v>-0.2353432887384428</v>
+        <v>-0.04094734053139382</v>
       </c>
       <c r="U19">
-        <v>-0.4612043030804567</v>
+        <v>0.005541379936312207</v>
       </c>
       <c r="V19" t="s">
         <v>6</v>
       </c>
       <c r="W19">
-        <v>4.737774216622949</v>
+        <v>4.827149341819798</v>
       </c>
       <c r="X19">
-        <v>1.041226624804049</v>
+        <v>0.7917433812247161</v>
       </c>
       <c r="Y19">
-        <v>0.6965475918188995</v>
+        <v>0.03540596059508161</v>
       </c>
       <c r="Z19">
-        <v>0.3642453953586904</v>
+        <v>0.2769703290780675</v>
       </c>
       <c r="AA19">
-        <v>0.2436686182664276</v>
+        <v>0.01238583206363622</v>
       </c>
       <c r="AB19">
         <v>0.6972159884595291</v>
       </c>
       <c r="AC19">
-        <v>72.46666497041721</v>
+        <v>83.16315746844765</v>
       </c>
       <c r="AD19" t="s">
         <v>81</v>
@@ -2289,25 +2289,25 @@
         <v>74</v>
       </c>
       <c r="C20">
-        <v>0.412</v>
+        <v>0.368</v>
       </c>
       <c r="D20">
-        <v>0.552</v>
+        <v>0.512</v>
       </c>
       <c r="E20">
-        <v>1.125104248703698</v>
+        <v>0.8003007397713651</v>
       </c>
       <c r="F20">
         <v>0.4</v>
       </c>
       <c r="G20">
-        <v>0.4778035103753786</v>
+        <v>0.4356836106718179</v>
       </c>
       <c r="J20" t="s">
         <v>4</v>
       </c>
       <c r="K20">
-        <v>1.125104248703698</v>
+        <v>0.8003007397713651</v>
       </c>
       <c r="L20">
         <v>0.8079772006265793</v>
@@ -2322,10 +2322,10 @@
         <v>77</v>
       </c>
       <c r="P20">
-        <v>0.9194716555837816</v>
+        <v>0.689041649067501</v>
       </c>
       <c r="Q20">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2334,37 +2334,37 @@
         <v>79</v>
       </c>
       <c r="T20">
-        <v>-0.2056325931199159</v>
+        <v>-0.1112590907038641</v>
       </c>
       <c r="U20">
-        <v>0.08052834441621837</v>
+        <v>0.310958350932499</v>
       </c>
       <c r="V20" t="s">
         <v>6</v>
       </c>
       <c r="W20">
-        <v>0.4778035103753786</v>
+        <v>0.4356836106718179</v>
       </c>
       <c r="X20">
-        <v>0.6473007383283189</v>
+        <v>0.3646171290995471</v>
       </c>
       <c r="Y20">
-        <v>0.1251042487036975</v>
+        <v>0.1996992602286349</v>
       </c>
       <c r="Z20">
-        <v>0.80113738088939</v>
+        <v>0.4512715566934187</v>
       </c>
       <c r="AA20">
-        <v>0.1548363599946635</v>
+        <v>0.247159523899647</v>
       </c>
       <c r="AB20">
         <v>1.346628667710966</v>
       </c>
       <c r="AC20">
-        <v>56.27431207716731</v>
+        <v>68.39760714610466</v>
       </c>
       <c r="AD20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:30">
@@ -2375,25 +2375,25 @@
         <v>74</v>
       </c>
       <c r="C21">
-        <v>0.216</v>
+        <v>0.236</v>
       </c>
       <c r="D21">
-        <v>0.18</v>
+        <v>0.184</v>
       </c>
       <c r="E21">
-        <v>0.01190808928740122</v>
+        <v>-0.05756181698960205</v>
       </c>
       <c r="F21">
         <v>0.2</v>
       </c>
       <c r="G21">
-        <v>0.1990790973320455</v>
+        <v>0.2115586961462879</v>
       </c>
       <c r="J21" t="s">
         <v>4</v>
       </c>
       <c r="K21">
-        <v>0.01190808928740122</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>0.421748166646455</v>
@@ -2408,10 +2408,10 @@
         <v>77</v>
       </c>
       <c r="P21">
-        <v>0.009731676495348316</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -2420,37 +2420,37 @@
         <v>79</v>
       </c>
       <c r="T21">
-        <v>-0.002176412792052908</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>-0.009731676495348316</v>
+        <v>0</v>
       </c>
       <c r="V21" t="s">
         <v>6</v>
       </c>
       <c r="W21">
-        <v>0.1990790973320455</v>
+        <v>0.2115586961462879</v>
       </c>
       <c r="X21">
-        <v>0.1871710080446443</v>
+        <v>0.2115586961462879</v>
       </c>
       <c r="Y21">
-        <v>0.01190808928740122</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>0.4437980360008223</v>
+        <v>0.5016232739753302</v>
       </c>
       <c r="AA21">
-        <v>0.02823507066335061</v>
+        <v>0</v>
       </c>
       <c r="AB21">
         <v>1.054370416616137</v>
       </c>
       <c r="AC21">
-        <v>74.20408390839145</v>
+        <v>72.17653967915379</v>
       </c>
       <c r="AD21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:30">
@@ -2461,25 +2461,25 @@
         <v>74</v>
       </c>
       <c r="C22">
-        <v>1.124</v>
+        <v>1.164</v>
       </c>
       <c r="D22">
-        <v>1.364</v>
+        <v>1.34</v>
       </c>
       <c r="E22">
-        <v>1.289478939532622</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="F22">
         <v>1.4</v>
       </c>
       <c r="G22">
-        <v>1.236806017786363</v>
+        <v>1.246724413043333</v>
       </c>
       <c r="J22" t="s">
         <v>4</v>
       </c>
       <c r="K22">
-        <v>1.289478939532622</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="L22">
         <v>0.9319718387197466</v>
@@ -2494,10 +2494,10 @@
         <v>77</v>
       </c>
       <c r="P22">
-        <v>1.053803980154308</v>
+        <v>1.06279383028951</v>
       </c>
       <c r="Q22">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -2506,37 +2506,37 @@
         <v>79</v>
       </c>
       <c r="T22">
-        <v>-0.2356749593783138</v>
+        <v>-0.1716086035201392</v>
       </c>
       <c r="U22">
-        <v>-0.05380398015430821</v>
+        <v>-0.06279383028951013</v>
       </c>
       <c r="V22" t="s">
         <v>6</v>
       </c>
       <c r="W22">
-        <v>1.236806017786363</v>
+        <v>1.246724413043333</v>
       </c>
       <c r="X22">
-        <v>0.05267292174625871</v>
+        <v>0.01232197923368372</v>
       </c>
       <c r="Y22">
-        <v>0.289478939532622</v>
+        <v>0.2344024338096493</v>
       </c>
       <c r="Z22">
-        <v>0.05651771819480694</v>
+        <v>0.0132214072590546</v>
       </c>
       <c r="AA22">
-        <v>0.3106091058827276</v>
+        <v>0.2515123569953024</v>
       </c>
       <c r="AB22">
         <v>1.035524265244163</v>
       </c>
       <c r="AC22">
-        <v>86.46333766795863</v>
+        <v>90.78980016577228</v>
       </c>
       <c r="AD22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -2547,25 +2547,25 @@
         <v>74</v>
       </c>
       <c r="C23">
-        <v>0.66</v>
+        <v>0.612</v>
       </c>
       <c r="D23">
-        <v>0.756</v>
+        <v>0.732</v>
       </c>
       <c r="E23">
-        <v>0.8217382316493707</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="F23">
         <v>0.6</v>
       </c>
       <c r="G23">
-        <v>0.7051224071145452</v>
+        <v>0.6684030088931816</v>
       </c>
       <c r="J23" t="s">
         <v>4</v>
       </c>
       <c r="K23">
-        <v>0.8217382316493707</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="L23">
         <v>1.559831022862906</v>
@@ -2580,49 +2580,49 @@
         <v>77</v>
       </c>
       <c r="P23">
-        <v>0.6715511146470821</v>
+        <v>0.2835868085528425</v>
       </c>
       <c r="Q23">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="s">
         <v>79</v>
       </c>
       <c r="T23">
-        <v>-0.1501871170022886</v>
+        <v>-0.04579057085721838</v>
       </c>
       <c r="U23">
-        <v>0.3284488853529179</v>
+        <v>-0.2835868085528425</v>
       </c>
       <c r="V23" t="s">
         <v>6</v>
       </c>
       <c r="W23">
-        <v>0.7051224071145452</v>
+        <v>0.6684030088931816</v>
       </c>
       <c r="X23">
-        <v>0.1166158245348254</v>
+        <v>0.3390256294831208</v>
       </c>
       <c r="Y23">
-        <v>0.1782617683506293</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="Z23">
-        <v>0.0747618317789252</v>
+        <v>0.2173476642751179</v>
       </c>
       <c r="AA23">
-        <v>0.1142827432829542</v>
+        <v>0.2111622185879616</v>
       </c>
       <c r="AB23">
         <v>1.299859185719089</v>
       </c>
       <c r="AC23">
-        <v>91.52169382676631</v>
+        <v>80.63940515159102</v>
       </c>
       <c r="AD23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:30">
@@ -2633,25 +2633,25 @@
         <v>74</v>
       </c>
       <c r="C24">
-        <v>1.868</v>
+        <v>1.9</v>
       </c>
       <c r="D24">
-        <v>1.492</v>
+        <v>1.54</v>
       </c>
       <c r="E24">
-        <v>1.186511751275934</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="F24">
         <v>1.6</v>
       </c>
       <c r="G24">
-        <v>1.691270572134697</v>
+        <v>1.730790973320455</v>
       </c>
       <c r="J24" t="s">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>1.186511751275934</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="L24">
         <v>1.157976831184469</v>
@@ -2666,10 +2666,10 @@
         <v>77</v>
       </c>
       <c r="P24">
-        <v>0.969655856843721</v>
+        <v>1.231964530182992</v>
       </c>
       <c r="Q24">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -2678,37 +2678,37 @@
         <v>79</v>
       </c>
       <c r="T24">
-        <v>-0.2168558944322125</v>
+        <v>-0.1989244824214469</v>
       </c>
       <c r="U24">
-        <v>0.03034414315627898</v>
+        <v>-0.2319645301829925</v>
       </c>
       <c r="V24" t="s">
         <v>6</v>
       </c>
       <c r="W24">
-        <v>1.691270572134697</v>
+        <v>1.730790973320455</v>
       </c>
       <c r="X24">
-        <v>0.5047588208587637</v>
+        <v>0.2999019607160154</v>
       </c>
       <c r="Y24">
-        <v>0.1865117512759336</v>
+        <v>0.4308890126044393</v>
       </c>
       <c r="Z24">
-        <v>0.4358971675991626</v>
+        <v>0.2589878766479743</v>
       </c>
       <c r="AA24">
-        <v>0.1610669110582764</v>
+        <v>0.3721050378561482</v>
       </c>
       <c r="AB24">
         <v>0.8271263079889064</v>
       </c>
       <c r="AC24">
-        <v>71.19792026130897</v>
+        <v>74.18717584194117</v>
       </c>
       <c r="AD24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:30">
@@ -2719,25 +2719,25 @@
         <v>74</v>
       </c>
       <c r="C25">
-        <v>0.652</v>
+        <v>0.676</v>
       </c>
       <c r="D25">
         <v>0.612</v>
       </c>
       <c r="E25">
-        <v>0.2977289224579263</v>
+        <v>-0.005331174175850051</v>
       </c>
       <c r="F25">
         <v>0.6</v>
       </c>
       <c r="G25">
-        <v>0.633198997035606</v>
+        <v>0.6459183952569697</v>
       </c>
       <c r="J25" t="s">
         <v>4</v>
       </c>
       <c r="K25">
-        <v>0.2977289224579263</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>1.005444112310955</v>
@@ -2752,10 +2752,10 @@
         <v>77</v>
       </c>
       <c r="P25">
-        <v>0.2433137245397242</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2764,37 +2764,37 @@
         <v>79</v>
       </c>
       <c r="T25">
-        <v>-0.05441519791820207</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>-0.2433137245397242</v>
+        <v>0</v>
       </c>
       <c r="V25" t="s">
         <v>6</v>
       </c>
       <c r="W25">
-        <v>0.633198997035606</v>
+        <v>0.6459183952569697</v>
       </c>
       <c r="X25">
-        <v>0.3354700745776797</v>
+        <v>0.6459183952569697</v>
       </c>
       <c r="Y25">
-        <v>0.2977289224579263</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>0.3336536267606375</v>
+        <v>0.642420983273117</v>
       </c>
       <c r="AA25">
-        <v>0.296116829182692</v>
+        <v>0</v>
       </c>
       <c r="AB25">
         <v>1.117160124789949</v>
       </c>
       <c r="AC25">
-        <v>72.57746240041317</v>
+        <v>65.86429881671735</v>
       </c>
       <c r="AD25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:30">
@@ -2805,25 +2805,25 @@
         <v>74</v>
       </c>
       <c r="C26">
-        <v>13.152</v>
+        <v>13.232</v>
       </c>
       <c r="D26">
-        <v>12.22</v>
+        <v>12.328</v>
       </c>
       <c r="E26">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="F26">
         <v>12.4</v>
       </c>
       <c r="G26">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="J26" t="s">
         <v>4</v>
       </c>
       <c r="K26">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="L26">
         <v>2.351026032651849</v>
@@ -2838,49 +2838,49 @@
         <v>77</v>
       </c>
       <c r="P26">
-        <v>9.132471991736034</v>
+        <v>9.674452691001546</v>
       </c>
       <c r="Q26">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S26" t="s">
         <v>79</v>
       </c>
       <c r="T26">
-        <v>-2.04240542473641</v>
+        <v>-1.562127356038731</v>
       </c>
       <c r="U26">
-        <v>-0.1324719917360344</v>
+        <v>0.3255473089984537</v>
       </c>
       <c r="V26" t="s">
         <v>6</v>
       </c>
       <c r="W26">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="X26">
-        <v>1.539059214457176</v>
+        <v>1.570517285964419</v>
       </c>
       <c r="Y26">
-        <v>2.174877416472444</v>
+        <v>1.236580047040277</v>
       </c>
       <c r="Z26">
-        <v>0.6546329955866917</v>
+        <v>0.6680135669076143</v>
       </c>
       <c r="AA26">
-        <v>0.9250758546553748</v>
+        <v>0.5259746297430284</v>
       </c>
       <c r="AB26">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC26">
-        <v>47.27029992542463</v>
+        <v>53.88597538332969</v>
       </c>
       <c r="AD26" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:30">
@@ -2891,25 +2891,25 @@
         <v>74</v>
       </c>
       <c r="C27">
-        <v>1.58</v>
+        <v>1.736</v>
       </c>
       <c r="D27">
-        <v>1.896</v>
+        <v>1.98</v>
       </c>
       <c r="E27">
-        <v>-0.7504271689963384</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="F27">
         <v>2.4</v>
       </c>
       <c r="G27">
-        <v>1.728527923418711</v>
+        <v>1.850686118082802</v>
       </c>
       <c r="J27" t="s">
         <v>4</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="L27">
         <v>1.736334852416627</v>
@@ -2924,10 +2924,10 @@
         <v>77</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>0.05816049090560802</v>
       </c>
       <c r="Q27">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2936,37 +2936,37 @@
         <v>79</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>-0.009391135269987715</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>-0.05816049090560802</v>
       </c>
       <c r="V27" t="s">
         <v>6</v>
       </c>
       <c r="W27">
-        <v>1.728527923418711</v>
+        <v>1.850686118082802</v>
       </c>
       <c r="X27">
-        <v>1.728527923418711</v>
+        <v>1.783134491907207</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="Z27">
-        <v>0.9955037883464413</v>
+        <v>1.026953118763609</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>0.03890472283130038</v>
       </c>
       <c r="AB27">
         <v>0.5601080169085895</v>
       </c>
       <c r="AC27">
-        <v>52.35737067882981</v>
+        <v>50.60417110498163</v>
       </c>
       <c r="AD27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:30">
@@ -2977,25 +2977,25 @@
         <v>74</v>
       </c>
       <c r="C28">
-        <v>0.192</v>
+        <v>0.164</v>
       </c>
       <c r="D28">
-        <v>0.3</v>
+        <v>0.268</v>
       </c>
       <c r="E28">
-        <v>0.851191504820574</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="F28">
         <v>0.2</v>
       </c>
       <c r="G28">
-        <v>0.2427627080038635</v>
+        <v>0.2128826077074241</v>
       </c>
       <c r="J28" t="s">
         <v>4</v>
       </c>
       <c r="K28">
-        <v>0.851191504820574</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="L28">
         <v>0.4925498319332764</v>
@@ -3010,10 +3010,10 @@
         <v>77</v>
       </c>
       <c r="P28">
-        <v>0.9871617767549565</v>
+        <v>0.7880676051329962</v>
       </c>
       <c r="Q28">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -3022,37 +3022,37 @@
         <v>79</v>
       </c>
       <c r="T28">
-        <v>0.1359702719343825</v>
+        <v>0.09755932516498467</v>
       </c>
       <c r="U28">
-        <v>0.01283822324504347</v>
+        <v>0.2119323948670038</v>
       </c>
       <c r="V28" t="s">
         <v>6</v>
       </c>
       <c r="W28">
-        <v>0.2427627080038635</v>
+        <v>0.2128826077074241</v>
       </c>
       <c r="X28">
-        <v>0.6084287968167106</v>
+        <v>0.4776256722605874</v>
       </c>
       <c r="Y28">
-        <v>0.148808495179426</v>
+        <v>0.3094917200319884</v>
       </c>
       <c r="Z28">
-        <v>1.23526343401358</v>
+        <v>0.9697002035020272</v>
       </c>
       <c r="AA28">
-        <v>0.3021186599442072</v>
+        <v>0.6283460067730039</v>
       </c>
       <c r="AB28">
         <v>1.231374579833191</v>
       </c>
       <c r="AC28">
-        <v>40.30628543413643</v>
+        <v>42.73182468197061</v>
       </c>
       <c r="AD28" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:30">
@@ -3063,25 +3063,25 @@
         <v>74</v>
       </c>
       <c r="C29">
-        <v>0.656</v>
+        <v>0.632</v>
       </c>
       <c r="D29">
-        <v>0.384</v>
+        <v>0.416</v>
       </c>
       <c r="E29">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F29">
         <v>0.4</v>
       </c>
       <c r="G29">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J29" t="s">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L29">
         <v>0.7620693762924241</v>
@@ -3096,10 +3096,10 @@
         <v>77</v>
       </c>
       <c r="P29">
-        <v>0.5063526117264946</v>
+        <v>0.7484613503089816</v>
       </c>
       <c r="Q29">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -3108,34 +3108,34 @@
         <v>79</v>
       </c>
       <c r="T29">
-        <v>0.06974429514224045</v>
+        <v>0.0926562439219849</v>
       </c>
       <c r="U29">
-        <v>0.4936473882735054</v>
+        <v>0.2515386496910184</v>
       </c>
       <c r="V29" t="s">
         <v>6</v>
       </c>
       <c r="W29">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="X29">
-        <v>0.09154486325786737</v>
+        <v>0.1253305223947238</v>
       </c>
       <c r="Y29">
-        <v>0.5633916834157459</v>
+        <v>0.3441948936130033</v>
       </c>
       <c r="Z29">
-        <v>0.1201266788901112</v>
+        <v>0.1644607778421363</v>
       </c>
       <c r="AA29">
-        <v>0.7392918557582336</v>
+        <v>0.4516582142265844</v>
       </c>
       <c r="AB29">
         <v>0.95258672036553</v>
       </c>
       <c r="AC29">
-        <v>71.40270081666996</v>
+        <v>76.72213858724069</v>
       </c>
       <c r="AD29" t="s">
         <v>81</v>
@@ -3182,10 +3182,10 @@
         <v>77</v>
       </c>
       <c r="P30">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="Q30">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -3194,10 +3194,10 @@
         <v>79</v>
       </c>
       <c r="T30">
-        <v>0.1597411054555158</v>
+        <v>0.141286249557361</v>
       </c>
       <c r="U30">
-        <v>-0.1597411054555158</v>
+        <v>-0.141286249557361</v>
       </c>
       <c r="V30" t="s">
         <v>6</v>
@@ -3226,25 +3226,25 @@
         <v>74</v>
       </c>
       <c r="C31">
-        <v>0.736</v>
+        <v>0.716</v>
       </c>
       <c r="D31">
-        <v>0.672</v>
+        <v>0.66</v>
       </c>
       <c r="E31">
-        <v>1.081403752400103</v>
+        <v>0.9608490161719081</v>
       </c>
       <c r="F31">
         <v>0.6</v>
       </c>
       <c r="G31">
-        <v>0.7059183952569696</v>
+        <v>0.6896785958498485</v>
       </c>
       <c r="J31" t="s">
         <v>4</v>
       </c>
       <c r="K31">
-        <v>1.081403752400103</v>
+        <v>0.9608490161719081</v>
       </c>
       <c r="L31">
         <v>0.3332002265469857</v>
@@ -3259,10 +3259,10 @@
         <v>77</v>
       </c>
       <c r="P31">
-        <v>1.254148383252238</v>
+        <v>1.096603770057717</v>
       </c>
       <c r="Q31">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -3271,37 +3271,37 @@
         <v>79</v>
       </c>
       <c r="T31">
-        <v>0.1727446308521352</v>
+        <v>0.135754753885809</v>
       </c>
       <c r="U31">
-        <v>-0.254148383252238</v>
+        <v>-0.09660377005771714</v>
       </c>
       <c r="V31" t="s">
         <v>6</v>
       </c>
       <c r="W31">
-        <v>0.7059183952569696</v>
+        <v>0.6896785958498485</v>
       </c>
       <c r="X31">
-        <v>0.3754853571431331</v>
+        <v>0.2711704203220596</v>
       </c>
       <c r="Y31">
-        <v>0.08140375240010278</v>
+        <v>0.0391509838280919</v>
       </c>
       <c r="Z31">
-        <v>1.126906067965067</v>
+        <v>0.813836242346675</v>
       </c>
       <c r="AA31">
-        <v>0.2443088146839053</v>
+        <v>0.1174998715751806</v>
       </c>
       <c r="AB31">
         <v>0.5553337109116429</v>
       </c>
       <c r="AC31">
-        <v>44.13147102701663</v>
+        <v>56.54584207939454</v>
       </c>
       <c r="AD31" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:30">
@@ -3312,25 +3312,25 @@
         <v>74</v>
       </c>
       <c r="C32">
-        <v>1.148</v>
+        <v>1.084</v>
       </c>
       <c r="D32">
-        <v>1.224</v>
+        <v>1.172</v>
       </c>
       <c r="E32">
-        <v>2.2065080011038</v>
+        <v>1.761149755943273</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>1.183721905632348</v>
+        <v>1.125362206521666</v>
       </c>
       <c r="J32" t="s">
         <v>4</v>
       </c>
       <c r="K32">
-        <v>2.2065080011038</v>
+        <v>1.761149755943273</v>
       </c>
       <c r="L32">
         <v>0.8500971208676269</v>
@@ -3345,46 +3345,46 @@
         <v>77</v>
       </c>
       <c r="P32">
-        <v>2.558978028396561</v>
+        <v>2.00997599986936</v>
       </c>
       <c r="Q32">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S32" t="s">
         <v>79</v>
       </c>
       <c r="T32">
-        <v>0.3524700272927612</v>
+        <v>0.2488262439260871</v>
       </c>
       <c r="U32">
-        <v>0.4410219716034391</v>
+        <v>-0.009975999869360042</v>
       </c>
       <c r="V32" t="s">
         <v>6</v>
       </c>
       <c r="W32">
-        <v>1.183721905632348</v>
+        <v>1.125362206521666</v>
       </c>
       <c r="X32">
-        <v>1.022786095471451</v>
+        <v>0.6357875494216065</v>
       </c>
       <c r="Y32">
-        <v>0.7934919988962004</v>
+        <v>0.2388502440567271</v>
       </c>
       <c r="Z32">
-        <v>1.203140288756154</v>
+        <v>0.7478998973349168</v>
       </c>
       <c r="AA32">
-        <v>0.933413347037743</v>
+        <v>0.2809681837446426</v>
       </c>
       <c r="AB32">
         <v>1.700194241735254</v>
       </c>
       <c r="AC32">
-        <v>32.99758334560023</v>
+        <v>55.73990894075605</v>
       </c>
       <c r="AD32" t="s">
         <v>84</v>
@@ -3398,25 +3398,25 @@
         <v>74</v>
       </c>
       <c r="C33">
-        <v>0.544</v>
+        <v>0.552</v>
       </c>
       <c r="D33">
-        <v>0.372</v>
+        <v>0.392</v>
       </c>
       <c r="E33">
-        <v>0.2302122475795285</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="F33">
         <v>0.4</v>
       </c>
       <c r="G33">
-        <v>0.4631556872531063</v>
+        <v>0.4767959881424244</v>
       </c>
       <c r="J33" t="s">
         <v>4</v>
       </c>
       <c r="K33">
-        <v>0.2302122475795285</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="L33">
         <v>0.3921195507989373</v>
@@ -3431,10 +3431,10 @@
         <v>77</v>
       </c>
       <c r="P33">
-        <v>0.2669866064972812</v>
+        <v>0.3085361649247209</v>
       </c>
       <c r="Q33">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -3443,37 +3443,37 @@
         <v>79</v>
       </c>
       <c r="T33">
-        <v>0.03677435891775274</v>
+        <v>0.03819542872082443</v>
       </c>
       <c r="U33">
-        <v>-0.2669866064972812</v>
+        <v>-0.3085361649247209</v>
       </c>
       <c r="V33" t="s">
         <v>6</v>
       </c>
       <c r="W33">
-        <v>0.4631556872531063</v>
+        <v>0.4767959881424244</v>
       </c>
       <c r="X33">
-        <v>0.2329434396735778</v>
+        <v>0.206455251938528</v>
       </c>
       <c r="Y33">
-        <v>0.2302122475795285</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="Z33">
-        <v>0.5940622934994169</v>
+        <v>0.526510987574781</v>
       </c>
       <c r="AA33">
-        <v>0.5870970909521719</v>
+        <v>0.6894344738819614</v>
       </c>
       <c r="AB33">
         <v>0.6535325846648956</v>
       </c>
       <c r="AC33">
-        <v>55.34275262590184</v>
+        <v>55.79230620253968</v>
       </c>
       <c r="AD33" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:30">
@@ -3484,25 +3484,25 @@
         <v>74</v>
       </c>
       <c r="C34">
-        <v>10.056</v>
+        <v>10.028</v>
       </c>
       <c r="D34">
-        <v>11.612</v>
+        <v>11.468</v>
       </c>
       <c r="E34">
-        <v>12.72721886527684</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="F34">
         <v>11.6</v>
       </c>
       <c r="G34">
-        <v>10.78735901531492</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="J34" t="s">
         <v>4</v>
       </c>
       <c r="K34">
-        <v>12.72721886527684</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="L34">
         <v>3.050242274051084</v>
@@ -3517,10 +3517,10 @@
         <v>77</v>
       </c>
       <c r="P34">
-        <v>14.76027887619046</v>
+        <v>15.15860750983988</v>
       </c>
       <c r="Q34">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R34">
         <v>15</v>
@@ -3529,37 +3529,37 @@
         <v>79</v>
       </c>
       <c r="T34">
-        <v>2.033060010913617</v>
+        <v>1.876569357081072</v>
       </c>
       <c r="U34">
-        <v>0.2397211238095416</v>
+        <v>-0.158607509839884</v>
       </c>
       <c r="V34" t="s">
         <v>6</v>
       </c>
       <c r="W34">
-        <v>10.78735901531492</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="X34">
-        <v>1.939859849961922</v>
+        <v>2.577202046040632</v>
       </c>
       <c r="Y34">
-        <v>2.272781134723159</v>
+        <v>1.717961847241188</v>
       </c>
       <c r="Z34">
-        <v>0.6359691052952189</v>
+        <v>0.8449171621432557</v>
       </c>
       <c r="AA34">
-        <v>0.7451149549850793</v>
+        <v>0.5632214404266095</v>
       </c>
       <c r="AB34">
         <v>0.544686120366265</v>
       </c>
       <c r="AC34">
-        <v>50.95791180581695</v>
+        <v>47.41063290551929</v>
       </c>
       <c r="AD34" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:30">
@@ -3570,25 +3570,25 @@
         <v>74</v>
       </c>
       <c r="C35">
-        <v>0.656</v>
+        <v>0.632</v>
       </c>
       <c r="D35">
-        <v>0.384</v>
+        <v>0.416</v>
       </c>
       <c r="E35">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F35">
         <v>0.4</v>
       </c>
       <c r="G35">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J35" t="s">
         <v>4</v>
       </c>
       <c r="K35">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L35">
         <v>0.7620693762924241</v>
@@ -3603,49 +3603,49 @@
         <v>77</v>
       </c>
       <c r="P35">
-        <v>0.5063526117264946</v>
+        <v>0.7484613503089816</v>
       </c>
       <c r="Q35">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="s">
         <v>79</v>
       </c>
       <c r="T35">
-        <v>0.06974429514224045</v>
+        <v>0.0926562439219849</v>
       </c>
       <c r="U35">
-        <v>-0.5063526117264946</v>
+        <v>0.2515386496910184</v>
       </c>
       <c r="V35" t="s">
         <v>6</v>
       </c>
       <c r="W35">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="X35">
-        <v>0.09154486325786737</v>
+        <v>0.1253305223947238</v>
       </c>
       <c r="Y35">
-        <v>0.4366083165842541</v>
+        <v>0.3441948936130033</v>
       </c>
       <c r="Z35">
-        <v>0.1201266788901112</v>
+        <v>0.1644607778421363</v>
       </c>
       <c r="AA35">
-        <v>0.5729246314927595</v>
+        <v>0.4516582142265844</v>
       </c>
       <c r="AB35">
         <v>0.95258672036553</v>
       </c>
       <c r="AC35">
-        <v>75.68380671977501</v>
+        <v>76.72213858724069</v>
       </c>
       <c r="AD35" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:30">
@@ -3662,7 +3662,7 @@
         <v>76</v>
       </c>
       <c r="R36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="s">
         <v>79</v>
@@ -3685,7 +3685,7 @@
         <v>76</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S37" t="s">
         <v>79</v>
@@ -3708,7 +3708,7 @@
         <v>76</v>
       </c>
       <c r="R38">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S38" t="s">
         <v>79</v>
@@ -3731,7 +3731,7 @@
         <v>76</v>
       </c>
       <c r="R39">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S39" t="s">
         <v>79</v>
@@ -3754,7 +3754,7 @@
         <v>76</v>
       </c>
       <c r="R40">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S40" t="s">
         <v>79</v>
@@ -3777,7 +3777,7 @@
         <v>76</v>
       </c>
       <c r="R41">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S41" t="s">
         <v>79</v>
@@ -3800,7 +3800,7 @@
         <v>76</v>
       </c>
       <c r="R42">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S42" t="s">
         <v>79</v>
@@ -3823,7 +3823,7 @@
         <v>76</v>
       </c>
       <c r="R43">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="S43" t="s">
         <v>79</v>
